--- a/08 - Excels/Open-LPs - pé.xlsx
+++ b/08 - Excels/Open-LPs - pé.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71100672-0DEA-48D3-AA5D-1190799CAF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB20793-2805-4FC5-A486-CF351FEA649A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,219 +20,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-044816</t>
-  </si>
-  <si>
-    <t>LP-045910</t>
-  </si>
-  <si>
-    <t>LP-046171</t>
-  </si>
-  <si>
-    <t>LP-046811</t>
-  </si>
-  <si>
-    <t>LP-047333</t>
-  </si>
-  <si>
-    <t>LP-047840</t>
-  </si>
-  <si>
-    <t>LP-048259</t>
-  </si>
-  <si>
-    <t>LP-048389</t>
-  </si>
-  <si>
-    <t>LP-048982</t>
-  </si>
-  <si>
-    <t>LP-049000</t>
-  </si>
-  <si>
-    <t>LP-049035</t>
-  </si>
-  <si>
-    <t>LP-049119</t>
-  </si>
-  <si>
-    <t>LP-049142</t>
-  </si>
-  <si>
-    <t>LP-049162</t>
-  </si>
-  <si>
-    <t>LP-049333</t>
-  </si>
-  <si>
-    <t>LP-049347</t>
-  </si>
-  <si>
-    <t>LP-049359</t>
-  </si>
-  <si>
-    <t>LP-049375</t>
-  </si>
-  <si>
-    <t>LP-049383</t>
-  </si>
-  <si>
-    <t>LP-049465</t>
-  </si>
-  <si>
-    <t>LP-049507</t>
-  </si>
-  <si>
-    <t>LP-049663</t>
-  </si>
-  <si>
-    <t>LP-049664</t>
-  </si>
-  <si>
-    <t>LP-049667</t>
-  </si>
-  <si>
-    <t>LP-049771</t>
-  </si>
-  <si>
-    <t>LP-049772</t>
-  </si>
-  <si>
-    <t>LP-049850</t>
-  </si>
-  <si>
-    <t>LP-549852</t>
-  </si>
-  <si>
-    <t>LP-049969</t>
-  </si>
-  <si>
-    <t>LP-050125</t>
-  </si>
-  <si>
-    <t>LP-050155</t>
-  </si>
-  <si>
-    <t>LP-050276</t>
-  </si>
-  <si>
-    <t>LP-050393</t>
-  </si>
-  <si>
-    <t>LP-050402</t>
-  </si>
-  <si>
-    <t>LP-050434</t>
-  </si>
-  <si>
-    <t>LP-050437</t>
-  </si>
-  <si>
-    <t>LP-050471</t>
-  </si>
-  <si>
-    <t>LP-050719</t>
-  </si>
-  <si>
-    <t>LP-050721</t>
-  </si>
-  <si>
-    <t>LP-050749</t>
-  </si>
-  <si>
-    <t>LP-050751</t>
-  </si>
-  <si>
-    <t>LP-050867</t>
-  </si>
-  <si>
-    <t>LP-051076</t>
-  </si>
-  <si>
-    <t>LP-051078</t>
-  </si>
-  <si>
-    <t>LP-051081</t>
-  </si>
-  <si>
-    <t>LP-051084</t>
-  </si>
-  <si>
-    <t>LP-051138</t>
-  </si>
-  <si>
-    <t>LP-051157</t>
-  </si>
-  <si>
-    <t>LP-051158</t>
-  </si>
-  <si>
-    <t>LP-051256</t>
-  </si>
-  <si>
-    <t>LP-051282</t>
-  </si>
-  <si>
-    <t>LP-051283</t>
-  </si>
-  <si>
-    <t>LP-051300</t>
-  </si>
-  <si>
-    <t>LP-051301</t>
-  </si>
-  <si>
-    <t>LP-051423</t>
-  </si>
-  <si>
-    <t>LP-051520</t>
-  </si>
-  <si>
-    <t>LP-051522</t>
-  </si>
-  <si>
-    <t>LP-051539</t>
-  </si>
-  <si>
-    <t>LP-051545</t>
-  </si>
-  <si>
-    <t>LP-051718</t>
-  </si>
-  <si>
-    <t>LP-051719</t>
-  </si>
-  <si>
-    <t>LP-051729</t>
-  </si>
-  <si>
-    <t>LP-052098</t>
-  </si>
-  <si>
-    <t>LP-049343</t>
-  </si>
-  <si>
-    <t>LP-049970</t>
-  </si>
-  <si>
-    <t>LP-050256</t>
-  </si>
-  <si>
-    <t>LP-050414</t>
-  </si>
-  <si>
-    <t>LP-051087</t>
-  </si>
-  <si>
-    <t>LP-051492</t>
-  </si>
-  <si>
-    <t>LP-051728</t>
+    <t>LP-049140</t>
+  </si>
+  <si>
+    <t>LP-050614</t>
+  </si>
+  <si>
+    <t>LP-050717</t>
+  </si>
+  <si>
+    <t>LP-051068</t>
+  </si>
+  <si>
+    <t>LP-051219</t>
+  </si>
+  <si>
+    <t>LP-051305</t>
+  </si>
+  <si>
+    <t>LP-051390</t>
+  </si>
+  <si>
+    <t>LP-051444</t>
+  </si>
+  <si>
+    <t>LP-051446</t>
+  </si>
+  <si>
+    <t>LP-051702</t>
+  </si>
+  <si>
+    <t>LP-051713</t>
+  </si>
+  <si>
+    <t>LP-051724</t>
+  </si>
+  <si>
+    <t>LP-051725</t>
+  </si>
+  <si>
+    <t>LP-051776</t>
+  </si>
+  <si>
+    <t>LP-052062</t>
+  </si>
+  <si>
+    <t>LP-052097</t>
+  </si>
+  <si>
+    <t>LP-052099</t>
+  </si>
+  <si>
+    <t>LP-052137</t>
+  </si>
+  <si>
+    <t>LP-052328</t>
+  </si>
+  <si>
+    <t>LP-052402</t>
+  </si>
+  <si>
+    <t>LP-051445</t>
+  </si>
+  <si>
+    <t>LP-051945</t>
+  </si>
+  <si>
+    <t>LP-052044</t>
   </si>
 </sst>
 </file>
@@ -595,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A71"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -648,312 +507,77 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs - pé.xlsx
+++ b/08 - Excels/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB20793-2805-4FC5-A486-CF351FEA649A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83D266E-0F7E-4F90-BBD2-4348BDD49A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,78 +20,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-049140</t>
-  </si>
-  <si>
-    <t>LP-050614</t>
-  </si>
-  <si>
-    <t>LP-050717</t>
-  </si>
-  <si>
-    <t>LP-051068</t>
-  </si>
-  <si>
-    <t>LP-051219</t>
-  </si>
-  <si>
-    <t>LP-051305</t>
-  </si>
-  <si>
-    <t>LP-051390</t>
-  </si>
-  <si>
-    <t>LP-051444</t>
-  </si>
-  <si>
-    <t>LP-051446</t>
-  </si>
-  <si>
-    <t>LP-051702</t>
-  </si>
-  <si>
-    <t>LP-051713</t>
-  </si>
-  <si>
-    <t>LP-051724</t>
-  </si>
-  <si>
-    <t>LP-051725</t>
-  </si>
-  <si>
-    <t>LP-051776</t>
-  </si>
-  <si>
-    <t>LP-052062</t>
-  </si>
-  <si>
-    <t>LP-052097</t>
-  </si>
-  <si>
-    <t>LP-052099</t>
-  </si>
-  <si>
-    <t>LP-052137</t>
-  </si>
-  <si>
-    <t>LP-052328</t>
-  </si>
-  <si>
-    <t>LP-052402</t>
-  </si>
-  <si>
-    <t>LP-051445</t>
-  </si>
-  <si>
-    <t>LP-051945</t>
-  </si>
-  <si>
-    <t>LP-052044</t>
+    <t>LP-045478</t>
+  </si>
+  <si>
+    <t>LP-045674</t>
+  </si>
+  <si>
+    <t>LP-048423</t>
+  </si>
+  <si>
+    <t>LP-048713</t>
+  </si>
+  <si>
+    <t>LP-048714</t>
+  </si>
+  <si>
+    <t>LP-049936</t>
+  </si>
+  <si>
+    <t>LP-050094</t>
+  </si>
+  <si>
+    <t>LP-050096</t>
+  </si>
+  <si>
+    <t>LP-050127</t>
+  </si>
+  <si>
+    <t>LP-050143</t>
+  </si>
+  <si>
+    <t>LP-050419</t>
+  </si>
+  <si>
+    <t>LP-051029</t>
+  </si>
+  <si>
+    <t>LP-051030</t>
+  </si>
+  <si>
+    <t>LP-051221</t>
+  </si>
+  <si>
+    <t>LP-051517</t>
+  </si>
+  <si>
+    <t>LP-051544</t>
+  </si>
+  <si>
+    <t>LP-051701</t>
+  </si>
+  <si>
+    <t>LP-052163</t>
   </si>
 </sst>
 </file>
@@ -454,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -507,77 +492,52 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs - pé.xlsx
+++ b/08 - Excels/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83D266E-0F7E-4F90-BBD2-4348BDD49A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4208A9F4-AC72-4035-8866-28411F68A786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/08 - Excels/Open-LPs - pé.xlsx
+++ b/08 - Excels/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4208A9F4-AC72-4035-8866-28411F68A786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A85438-7128-4003-A403-C36E17723E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,63 +20,120 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-045478</t>
-  </si>
-  <si>
-    <t>LP-045674</t>
-  </si>
-  <si>
-    <t>LP-048423</t>
-  </si>
-  <si>
-    <t>LP-048713</t>
-  </si>
-  <si>
-    <t>LP-048714</t>
-  </si>
-  <si>
-    <t>LP-049936</t>
-  </si>
-  <si>
-    <t>LP-050094</t>
-  </si>
-  <si>
-    <t>LP-050096</t>
-  </si>
-  <si>
-    <t>LP-050127</t>
-  </si>
-  <si>
-    <t>LP-050143</t>
-  </si>
-  <si>
-    <t>LP-050419</t>
-  </si>
-  <si>
-    <t>LP-051029</t>
-  </si>
-  <si>
-    <t>LP-051030</t>
-  </si>
-  <si>
-    <t>LP-051221</t>
-  </si>
-  <si>
-    <t>LP-051517</t>
-  </si>
-  <si>
-    <t>LP-051544</t>
-  </si>
-  <si>
-    <t>LP-051701</t>
-  </si>
-  <si>
-    <t>LP-052163</t>
+    <t>LP-049001</t>
+  </si>
+  <si>
+    <t>LP-049049</t>
+  </si>
+  <si>
+    <t>LP-049156</t>
+  </si>
+  <si>
+    <t>LP-049495</t>
+  </si>
+  <si>
+    <t>LP-049506</t>
+  </si>
+  <si>
+    <t>LP-049839</t>
+  </si>
+  <si>
+    <t>LP-049937</t>
+  </si>
+  <si>
+    <t>LP-049966</t>
+  </si>
+  <si>
+    <t>LP-050135</t>
+  </si>
+  <si>
+    <t>LP-050228</t>
+  </si>
+  <si>
+    <t>LP-050311</t>
+  </si>
+  <si>
+    <t>LP-050398</t>
+  </si>
+  <si>
+    <t>LP-050408</t>
+  </si>
+  <si>
+    <t>LP-050605</t>
+  </si>
+  <si>
+    <t>LP-050663</t>
+  </si>
+  <si>
+    <t>LP-050718</t>
+  </si>
+  <si>
+    <t>LP-051028</t>
+  </si>
+  <si>
+    <t>LP-051486</t>
+  </si>
+  <si>
+    <t>LP-051518</t>
+  </si>
+  <si>
+    <t>LP-051700</t>
+  </si>
+  <si>
+    <t>LP-051714</t>
+  </si>
+  <si>
+    <t>LP-051723</t>
+  </si>
+  <si>
+    <t>LP-051777</t>
+  </si>
+  <si>
+    <t>LP-052125</t>
+  </si>
+  <si>
+    <t>LP-052126</t>
+  </si>
+  <si>
+    <t>LP-052127</t>
+  </si>
+  <si>
+    <t>LP-052139</t>
+  </si>
+  <si>
+    <t>LP-052200</t>
+  </si>
+  <si>
+    <t>LP-052380</t>
+  </si>
+  <si>
+    <t>LP-052401</t>
+  </si>
+  <si>
+    <t>LP-052403</t>
+  </si>
+  <si>
+    <t>LP-052404</t>
+  </si>
+  <si>
+    <t>LP-052405</t>
+  </si>
+  <si>
+    <t>LP-052549</t>
+  </si>
+  <si>
+    <t>LP-052753</t>
+  </si>
+  <si>
+    <t>LP-051376</t>
+  </si>
+  <si>
+    <t>LP-052226</t>
   </si>
 </sst>
 </file>
@@ -439,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -537,7 +594,102 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs - pé.xlsx
+++ b/08 - Excels/Open-LPs - pé.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\08 - Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A85438-7128-4003-A403-C36E17723E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA10D74A-9726-4A03-960C-001DD27F0BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,120 +20,288 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-049001</t>
-  </si>
-  <si>
-    <t>LP-049049</t>
-  </si>
-  <si>
-    <t>LP-049156</t>
-  </si>
-  <si>
-    <t>LP-049495</t>
-  </si>
-  <si>
-    <t>LP-049506</t>
-  </si>
-  <si>
-    <t>LP-049839</t>
-  </si>
-  <si>
-    <t>LP-049937</t>
-  </si>
-  <si>
-    <t>LP-049966</t>
-  </si>
-  <si>
-    <t>LP-050135</t>
-  </si>
-  <si>
-    <t>LP-050228</t>
-  </si>
-  <si>
-    <t>LP-050311</t>
-  </si>
-  <si>
-    <t>LP-050398</t>
-  </si>
-  <si>
-    <t>LP-050408</t>
-  </si>
-  <si>
-    <t>LP-050605</t>
-  </si>
-  <si>
-    <t>LP-050663</t>
-  </si>
-  <si>
-    <t>LP-050718</t>
-  </si>
-  <si>
-    <t>LP-051028</t>
-  </si>
-  <si>
-    <t>LP-051486</t>
-  </si>
-  <si>
-    <t>LP-051518</t>
-  </si>
-  <si>
-    <t>LP-051700</t>
-  </si>
-  <si>
-    <t>LP-051714</t>
-  </si>
-  <si>
-    <t>LP-051723</t>
-  </si>
-  <si>
-    <t>LP-051777</t>
-  </si>
-  <si>
-    <t>LP-052125</t>
-  </si>
-  <si>
-    <t>LP-052126</t>
-  </si>
-  <si>
-    <t>LP-052127</t>
-  </si>
-  <si>
-    <t>LP-052139</t>
-  </si>
-  <si>
-    <t>LP-052200</t>
-  </si>
-  <si>
-    <t>LP-052380</t>
-  </si>
-  <si>
-    <t>LP-052401</t>
-  </si>
-  <si>
-    <t>LP-052403</t>
-  </si>
-  <si>
-    <t>LP-052404</t>
-  </si>
-  <si>
-    <t>LP-052405</t>
-  </si>
-  <si>
-    <t>LP-052549</t>
-  </si>
-  <si>
-    <t>LP-052753</t>
-  </si>
-  <si>
-    <t>LP-051376</t>
-  </si>
-  <si>
-    <t>LP-052226</t>
+    <t>LP-048172</t>
+  </si>
+  <si>
+    <t>LP-048199</t>
+  </si>
+  <si>
+    <t>LP-049318</t>
+  </si>
+  <si>
+    <t>LP-049461</t>
+  </si>
+  <si>
+    <t>LP-049647</t>
+  </si>
+  <si>
+    <t>LP-049932</t>
+  </si>
+  <si>
+    <t>LP-050132</t>
+  </si>
+  <si>
+    <t>LP-050244</t>
+  </si>
+  <si>
+    <t>LP-050317</t>
+  </si>
+  <si>
+    <t>LP-050410</t>
+  </si>
+  <si>
+    <t>LP-050429</t>
+  </si>
+  <si>
+    <t>LP-050430</t>
+  </si>
+  <si>
+    <t>LP-050456</t>
+  </si>
+  <si>
+    <t>LP-050465</t>
+  </si>
+  <si>
+    <t>LP-050466</t>
+  </si>
+  <si>
+    <t>LP-050468</t>
+  </si>
+  <si>
+    <t>LP-050479</t>
+  </si>
+  <si>
+    <t>LP-050529</t>
+  </si>
+  <si>
+    <t>LP-050731</t>
+  </si>
+  <si>
+    <t>LP-050736</t>
+  </si>
+  <si>
+    <t>LP-050753</t>
+  </si>
+  <si>
+    <t>LP-050855</t>
+  </si>
+  <si>
+    <t>LP-050856</t>
+  </si>
+  <si>
+    <t>LP-051042</t>
+  </si>
+  <si>
+    <t>LP-051069</t>
+  </si>
+  <si>
+    <t>LP-051217</t>
+  </si>
+  <si>
+    <t>LP-051220</t>
+  </si>
+  <si>
+    <t>LP-051281</t>
+  </si>
+  <si>
+    <t>LP-051284</t>
+  </si>
+  <si>
+    <t>LP-051297</t>
+  </si>
+  <si>
+    <t>LP-051353</t>
+  </si>
+  <si>
+    <t>LP-051369</t>
+  </si>
+  <si>
+    <t>LP-051388</t>
+  </si>
+  <si>
+    <t>LP-051395</t>
+  </si>
+  <si>
+    <t>LP-051425</t>
+  </si>
+  <si>
+    <t>LP-051432</t>
+  </si>
+  <si>
+    <t>LP-051434</t>
+  </si>
+  <si>
+    <t>LP-051448</t>
+  </si>
+  <si>
+    <t>LP-051519</t>
+  </si>
+  <si>
+    <t>LP-051540</t>
+  </si>
+  <si>
+    <t>LP-051541</t>
+  </si>
+  <si>
+    <t>LP-051543</t>
+  </si>
+  <si>
+    <t>LP-051705</t>
+  </si>
+  <si>
+    <t>LP-052138</t>
+  </si>
+  <si>
+    <t>LP-052141</t>
+  </si>
+  <si>
+    <t>LP-052160</t>
+  </si>
+  <si>
+    <t>LP-052199</t>
+  </si>
+  <si>
+    <t>LP-052308</t>
+  </si>
+  <si>
+    <t>LP-052309</t>
+  </si>
+  <si>
+    <t>LP-052312</t>
+  </si>
+  <si>
+    <t>LP-052326</t>
+  </si>
+  <si>
+    <t>LP-052372</t>
+  </si>
+  <si>
+    <t>LP-052386</t>
+  </si>
+  <si>
+    <t>LP-052400</t>
+  </si>
+  <si>
+    <t>LP-052406</t>
+  </si>
+  <si>
+    <t>LP-052623</t>
+  </si>
+  <si>
+    <t>LP-052680</t>
+  </si>
+  <si>
+    <t>LP-052681</t>
+  </si>
+  <si>
+    <t>LP-052720</t>
+  </si>
+  <si>
+    <t>LP-052721</t>
+  </si>
+  <si>
+    <t>LP-052726</t>
+  </si>
+  <si>
+    <t>LP-052727</t>
+  </si>
+  <si>
+    <t>LP-052728</t>
+  </si>
+  <si>
+    <t>LP-052729</t>
+  </si>
+  <si>
+    <t>LP-052749</t>
+  </si>
+  <si>
+    <t>LP-052752</t>
+  </si>
+  <si>
+    <t>LP-052754</t>
+  </si>
+  <si>
+    <t>LP-052756</t>
+  </si>
+  <si>
+    <t>LP-052773</t>
+  </si>
+  <si>
+    <t>LP-052978</t>
+  </si>
+  <si>
+    <t>LP-053040</t>
+  </si>
+  <si>
+    <t>LP-053105</t>
+  </si>
+  <si>
+    <t>LP-048143</t>
+  </si>
+  <si>
+    <t>LP-049316</t>
+  </si>
+  <si>
+    <t>LP-049325</t>
+  </si>
+  <si>
+    <t>LP-049452</t>
+  </si>
+  <si>
+    <t>LP-049709</t>
+  </si>
+  <si>
+    <t>LP-049953</t>
+  </si>
+  <si>
+    <t>LP-050404</t>
+  </si>
+  <si>
+    <t>LP-050460</t>
+  </si>
+  <si>
+    <t>LP-050461</t>
+  </si>
+  <si>
+    <t>LP-050469</t>
+  </si>
+  <si>
+    <t>LP-051019</t>
+  </si>
+  <si>
+    <t>LP-051097</t>
+  </si>
+  <si>
+    <t>LP-051391</t>
+  </si>
+  <si>
+    <t>LP-051431</t>
+  </si>
+  <si>
+    <t>LP-051449</t>
+  </si>
+  <si>
+    <t>LP-051712</t>
+  </si>
+  <si>
+    <t>LP-051716</t>
+  </si>
+  <si>
+    <t>LP-052122</t>
+  </si>
+  <si>
+    <t>LP-052311</t>
+  </si>
+  <si>
+    <t>LP-052381</t>
+  </si>
+  <si>
+    <t>LP-052722</t>
   </si>
 </sst>
 </file>
@@ -496,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -509,187 +677,467 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/08 - Excels/Open-LPs - pé.xlsx
+++ b/08 - Excels/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\08 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA10D74A-9726-4A03-960C-001DD27F0BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2AFF17-3649-413F-B45B-6B05E85C319D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,288 +20,159 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-048172</t>
-  </si>
-  <si>
-    <t>LP-048199</t>
-  </si>
-  <si>
-    <t>LP-049318</t>
-  </si>
-  <si>
-    <t>LP-049461</t>
-  </si>
-  <si>
-    <t>LP-049647</t>
-  </si>
-  <si>
-    <t>LP-049932</t>
-  </si>
-  <si>
-    <t>LP-050132</t>
-  </si>
-  <si>
-    <t>LP-050244</t>
-  </si>
-  <si>
-    <t>LP-050317</t>
-  </si>
-  <si>
-    <t>LP-050410</t>
-  </si>
-  <si>
-    <t>LP-050429</t>
-  </si>
-  <si>
-    <t>LP-050430</t>
-  </si>
-  <si>
-    <t>LP-050456</t>
-  </si>
-  <si>
-    <t>LP-050465</t>
-  </si>
-  <si>
-    <t>LP-050466</t>
-  </si>
-  <si>
-    <t>LP-050468</t>
-  </si>
-  <si>
-    <t>LP-050479</t>
-  </si>
-  <si>
-    <t>LP-050529</t>
-  </si>
-  <si>
-    <t>LP-050731</t>
-  </si>
-  <si>
-    <t>LP-050736</t>
-  </si>
-  <si>
-    <t>LP-050753</t>
-  </si>
-  <si>
-    <t>LP-050855</t>
-  </si>
-  <si>
-    <t>LP-050856</t>
-  </si>
-  <si>
-    <t>LP-051042</t>
-  </si>
-  <si>
-    <t>LP-051069</t>
-  </si>
-  <si>
-    <t>LP-051217</t>
-  </si>
-  <si>
-    <t>LP-051220</t>
-  </si>
-  <si>
-    <t>LP-051281</t>
-  </si>
-  <si>
-    <t>LP-051284</t>
-  </si>
-  <si>
-    <t>LP-051297</t>
-  </si>
-  <si>
-    <t>LP-051353</t>
-  </si>
-  <si>
-    <t>LP-051369</t>
-  </si>
-  <si>
-    <t>LP-051388</t>
-  </si>
-  <si>
-    <t>LP-051395</t>
-  </si>
-  <si>
-    <t>LP-051425</t>
-  </si>
-  <si>
-    <t>LP-051432</t>
-  </si>
-  <si>
-    <t>LP-051434</t>
-  </si>
-  <si>
-    <t>LP-051448</t>
-  </si>
-  <si>
-    <t>LP-051519</t>
-  </si>
-  <si>
-    <t>LP-051540</t>
-  </si>
-  <si>
-    <t>LP-051541</t>
-  </si>
-  <si>
-    <t>LP-051543</t>
-  </si>
-  <si>
-    <t>LP-051705</t>
-  </si>
-  <si>
-    <t>LP-052138</t>
-  </si>
-  <si>
-    <t>LP-052141</t>
-  </si>
-  <si>
-    <t>LP-052160</t>
-  </si>
-  <si>
-    <t>LP-052199</t>
-  </si>
-  <si>
-    <t>LP-052308</t>
-  </si>
-  <si>
-    <t>LP-052309</t>
-  </si>
-  <si>
-    <t>LP-052312</t>
-  </si>
-  <si>
-    <t>LP-052326</t>
-  </si>
-  <si>
-    <t>LP-052372</t>
-  </si>
-  <si>
-    <t>LP-052386</t>
-  </si>
-  <si>
-    <t>LP-052400</t>
-  </si>
-  <si>
-    <t>LP-052406</t>
-  </si>
-  <si>
-    <t>LP-052623</t>
-  </si>
-  <si>
-    <t>LP-052680</t>
-  </si>
-  <si>
-    <t>LP-052681</t>
-  </si>
-  <si>
-    <t>LP-052720</t>
-  </si>
-  <si>
-    <t>LP-052721</t>
-  </si>
-  <si>
-    <t>LP-052726</t>
-  </si>
-  <si>
-    <t>LP-052727</t>
-  </si>
-  <si>
-    <t>LP-052728</t>
-  </si>
-  <si>
-    <t>LP-052729</t>
-  </si>
-  <si>
-    <t>LP-052749</t>
-  </si>
-  <si>
-    <t>LP-052752</t>
-  </si>
-  <si>
-    <t>LP-052754</t>
-  </si>
-  <si>
-    <t>LP-052756</t>
-  </si>
-  <si>
-    <t>LP-052773</t>
-  </si>
-  <si>
-    <t>LP-052978</t>
-  </si>
-  <si>
-    <t>LP-053040</t>
-  </si>
-  <si>
-    <t>LP-053105</t>
-  </si>
-  <si>
-    <t>LP-048143</t>
-  </si>
-  <si>
-    <t>LP-049316</t>
-  </si>
-  <si>
-    <t>LP-049325</t>
-  </si>
-  <si>
-    <t>LP-049452</t>
-  </si>
-  <si>
-    <t>LP-049709</t>
-  </si>
-  <si>
-    <t>LP-049953</t>
-  </si>
-  <si>
-    <t>LP-050404</t>
-  </si>
-  <si>
-    <t>LP-050460</t>
-  </si>
-  <si>
-    <t>LP-050461</t>
-  </si>
-  <si>
-    <t>LP-050469</t>
-  </si>
-  <si>
-    <t>LP-051019</t>
-  </si>
-  <si>
-    <t>LP-051097</t>
-  </si>
-  <si>
-    <t>LP-051391</t>
-  </si>
-  <si>
-    <t>LP-051431</t>
-  </si>
-  <si>
-    <t>LP-051449</t>
-  </si>
-  <si>
-    <t>LP-051712</t>
-  </si>
-  <si>
-    <t>LP-051716</t>
-  </si>
-  <si>
-    <t>LP-052122</t>
-  </si>
-  <si>
-    <t>LP-052311</t>
-  </si>
-  <si>
-    <t>LP-052381</t>
-  </si>
-  <si>
-    <t>LP-052722</t>
+    <t>LP-048805</t>
+  </si>
+  <si>
+    <t>LP-048964</t>
+  </si>
+  <si>
+    <t>LP-049027</t>
+  </si>
+  <si>
+    <t>LP-049395</t>
+  </si>
+  <si>
+    <t>LP-049396</t>
+  </si>
+  <si>
+    <t>LP-049943</t>
+  </si>
+  <si>
+    <t>LP-050090</t>
+  </si>
+  <si>
+    <t>LP-050470</t>
+  </si>
+  <si>
+    <t>LP-050740</t>
+  </si>
+  <si>
+    <t>LP-051051</t>
+  </si>
+  <si>
+    <t>LP-051218</t>
+  </si>
+  <si>
+    <t>LP-051303</t>
+  </si>
+  <si>
+    <t>LP-051304</t>
+  </si>
+  <si>
+    <t>LP-051389</t>
+  </si>
+  <si>
+    <t>LP-051521</t>
+  </si>
+  <si>
+    <t>LP-051535</t>
+  </si>
+  <si>
+    <t>LP-051707</t>
+  </si>
+  <si>
+    <t>LP-051810</t>
+  </si>
+  <si>
+    <t>LP-052015</t>
+  </si>
+  <si>
+    <t>LP-052116</t>
+  </si>
+  <si>
+    <t>LP-052161</t>
+  </si>
+  <si>
+    <t>LP-052306</t>
+  </si>
+  <si>
+    <t>LP-052310</t>
+  </si>
+  <si>
+    <t>LP-052396</t>
+  </si>
+  <si>
+    <t>LP-052625</t>
+  </si>
+  <si>
+    <t>LP-052714</t>
+  </si>
+  <si>
+    <t>LP-052723</t>
+  </si>
+  <si>
+    <t>LP-052746</t>
+  </si>
+  <si>
+    <t>LP-052788</t>
+  </si>
+  <si>
+    <t>LP-052789</t>
+  </si>
+  <si>
+    <t>LP-053081</t>
+  </si>
+  <si>
+    <t>LP-053082</t>
+  </si>
+  <si>
+    <t>LP-053240</t>
+  </si>
+  <si>
+    <t>LP-047527</t>
+  </si>
+  <si>
+    <t>LP-049460</t>
+  </si>
+  <si>
+    <t>LP-050669</t>
+  </si>
+  <si>
+    <t>LP-050684</t>
+  </si>
+  <si>
+    <t>LP-050980</t>
+  </si>
+  <si>
+    <t>LP-051044</t>
+  </si>
+  <si>
+    <t>LP-051096</t>
+  </si>
+  <si>
+    <t>LP-051299</t>
+  </si>
+  <si>
+    <t>LP-051348</t>
+  </si>
+  <si>
+    <t>LP-051427</t>
+  </si>
+  <si>
+    <t>LP-051512</t>
+  </si>
+  <si>
+    <t>LP-051523</t>
+  </si>
+  <si>
+    <t>LP-051726</t>
+  </si>
+  <si>
+    <t>LP-051727</t>
+  </si>
+  <si>
+    <t>LP-052013</t>
+  </si>
+  <si>
+    <t>LP-052901</t>
+  </si>
+  <si>
+    <t>LP-052976</t>
   </si>
 </sst>
 </file>
@@ -664,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A94"/>
+  <dimension ref="A1:A51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -677,7 +548,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -692,72 +563,72 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -767,22 +638,22 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -792,352 +663,137 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
